--- a/Cement_Firms.xlsx
+++ b/Cement_Firms.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rajesh_sharma/Desktop/Yale_ Harvard Data Course/YALE/Capstone/Project Outline/Final with:out DEA/Final/In_ R (Final)/Results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rajesh_sharma/Desktop/Yale_ Harvard Data Course/YALE/Capstone/Project Outline/Final with:out DEA/Final/In_ R (Final)/Results/Final_ for GitHub/Rajesh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A274389-5707-1D4D-96AE-123699775FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3454927C-461D-4A49-9875-D61FAF5E81AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="1380" windowWidth="28560" windowHeight="16100" xr2:uid="{B8E404B3-3F42-F646-AAD0-F486966E2FB7}"/>
+    <workbookView xWindow="240" yWindow="820" windowWidth="28560" windowHeight="16100" xr2:uid="{B8E404B3-3F42-F646-AAD0-F486966E2FB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Data_set" sheetId="2" r:id="rId1"/>
